--- a/CLNDC.xlsx
+++ b/CLNDC.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="103">
   <si>
     <t>NOM COMERCIAL</t>
   </si>
@@ -295,13 +295,46 @@
   </si>
   <si>
     <t>LEJDAR TRAVEL</t>
+  </si>
+  <si>
+    <t>ATLAS VOYAGES</t>
+  </si>
+  <si>
+    <t>KADI TOURS</t>
+  </si>
+  <si>
+    <t>411ND013</t>
+  </si>
+  <si>
+    <t>ANAPIA TRAVEL SERVICES</t>
+  </si>
+  <si>
+    <t>OPTIMA BOOKING SERVICES</t>
+  </si>
+  <si>
+    <t>SARL HELLO TRAVEL</t>
+  </si>
+  <si>
+    <t>SARL SAB NOUR LIL SAYAHA WA AL ASFAR</t>
+  </si>
+  <si>
+    <t>HELLO TRAVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">411ND014      </t>
+  </si>
+  <si>
+    <t>TOURING ALGERIA TRANSPORT TRAVEL</t>
+  </si>
+  <si>
+    <t>CALTAM  / TOURING ALGERIA TRANSPORT TRAVEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +344,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -384,7 +423,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -401,12 +440,46 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -724,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -1428,6 +1501,118 @@
         <v>41100007</v>
       </c>
     </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="1">
+        <v>411</v>
+      </c>
+      <c r="D48">
+        <v>41100105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="1">
+        <v>411</v>
+      </c>
+      <c r="D49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A50" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="1">
+        <v>411</v>
+      </c>
+      <c r="D50" s="11">
+        <v>41100444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A51" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="1">
+        <v>411</v>
+      </c>
+      <c r="D51" s="11">
+        <v>41100105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A52" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="1">
+        <v>411</v>
+      </c>
+      <c r="D52" s="11">
+        <v>41100006</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A53" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="1">
+        <v>411</v>
+      </c>
+      <c r="D53">
+        <v>41100164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A54" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="1">
+        <v>411</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A55" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="1">
+        <v>411</v>
+      </c>
+      <c r="D55" s="11">
+        <v>41100327</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D44">
     <sortState ref="A2:D45">
@@ -1435,9 +1620,15 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D45 D48:D1048576">
+  <conditionalFormatting sqref="D1:D45 D57:D1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D49 D57:D1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
